--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="320">
   <si>
     <t xml:space="preserve">EVENT CUSTOM SLIDERS</t>
   </si>
@@ -569,6 +569,18 @@
     <t xml:space="preserve">sends &lt;cmd&gt; (1byte in HEX) and optional &lt;value&gt; (0-65535) and &lt;param&gt; (0-255) to Orbiter</t>
   </si>
   <si>
+    <t xml:space="preserve">lebrew(&lt;msg&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sends &lt;msg&gt; to the BLE connected RoastSeeNEXT device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sr900(&lt;target&gt;[,&lt;value&gt;])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sends &lt;target&gt; command like ‘heat’ and ‘fan’, with optional int &lt;value&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">shellyrelay(n,b)</t>
   </si>
   <si>
@@ -764,6 +776,30 @@
   </si>
   <si>
     <t xml:space="preserve">sets the PID lookahead in seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidPositiveTargetMin(&lt;n&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the PID positive target range minium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidPositiveTargetMax(&lt;n&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the PID positive target range maximum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidNegativeTargetMin(&lt;n&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the PID negative target range minium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidNegativeTargetMax(&lt;n&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the PID negative target range maximum</t>
   </si>
   <si>
     <t xml:space="preserve">replayLookahead(&lt;int&gt;)</t>
@@ -1016,12 +1052,6 @@
   </si>
   <si>
     <t xml:space="preserve">shows/hides the events of the background profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upload2RoastHubs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upload current loaded profile to RoastHubs</t>
   </si>
   <si>
     <t xml:space="preserve">RC Command</t>
@@ -1249,37 +1279,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1353,7 +1383,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.27"/>
@@ -1468,8 +1498,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
-  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.54"/>
@@ -2070,11 +2100,8 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>167</v>
@@ -2082,31 +2109,34 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="2" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="B76" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="2" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="2" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>172</v>
@@ -2145,50 +2175,50 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="C84" s="1" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="1" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="1" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>187</v>
       </c>
+      <c r="B87" s="2"/>
       <c r="C87" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -2205,26 +2235,26 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="2" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="2" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2351,7 +2381,7 @@
       <c r="B108" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="3" t="s">
         <v>228</v>
       </c>
     </row>
@@ -2359,7 +2389,7 @@
       <c r="B109" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="3" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2367,7 +2397,7 @@
       <c r="B110" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="3" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2410,7 +2440,6 @@
       <c r="C115" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="2" t="s">
@@ -2459,6 +2488,7 @@
       <c r="C121" s="1" t="s">
         <v>254</v>
       </c>
+      <c r="D121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="2" t="s">
@@ -2549,49 +2579,49 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="s">
+      <c r="B133" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C137" s="1" t="s">
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="2" t="s">
         <v>288</v>
       </c>
@@ -2617,98 +2647,140 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="2" t="s">
-        <v>101</v>
+        <v>294</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="2" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="B145" s="2" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="2" t="s">
-        <v>302</v>
+        <v>101</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="2" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="B148" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="2" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>118</v>
+        <v>309</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="B150" s="2" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>168</v>
+        <v>311</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="310">
   <si>
     <t xml:space="preserve">EVENT CUSTOM SLIDERS</t>
   </si>
@@ -569,18 +569,6 @@
     <t xml:space="preserve">sends &lt;cmd&gt; (1byte in HEX) and optional &lt;value&gt; (0-65535) and &lt;param&gt; (0-255) to Orbiter</t>
   </si>
   <si>
-    <t xml:space="preserve">lebrew(&lt;msg&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sends &lt;msg&gt; to the BLE connected RoastSeeNEXT device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sr900(&lt;target&gt;[,&lt;value&gt;])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sends &lt;target&gt; command like ‘heat’ and ‘fan’, with optional int &lt;value&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">shellyrelay(n,b)</t>
   </si>
   <si>
@@ -776,30 +764,6 @@
   </si>
   <si>
     <t xml:space="preserve">sets the PID lookahead in seconds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pidPositiveTargetMin(&lt;n&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sets the PID positive target range minium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pidPositiveTargetMax(&lt;n&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sets the PID positive target range maximum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pidNegativeTargetMin(&lt;n&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sets the PID negative target range minium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pidNegativeTargetMax(&lt;n&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sets the PID negative target range maximum</t>
   </si>
   <si>
     <t xml:space="preserve">replayLookahead(&lt;int&gt;)</t>
@@ -1052,6 +1016,12 @@
   </si>
   <si>
     <t xml:space="preserve">shows/hides the events of the background profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upload2RoastHubs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upload current loaded profile to RoastHubs</t>
   </si>
   <si>
     <t xml:space="preserve">RC Command</t>
@@ -1279,37 +1249,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1383,7 +1353,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.27"/>
@@ -1498,8 +1468,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D151"/>
+  <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.54"/>
@@ -2100,8 +2070,11 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="B74" s="2" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>167</v>
@@ -2109,34 +2082,31 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="2" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="2" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>172</v>
@@ -2175,50 +2145,50 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="2" t="s">
-        <v>183</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="1" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="1" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="1" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B87" s="2"/>
       <c r="C87" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -2235,26 +2205,26 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="2" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="2" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2381,7 +2351,7 @@
       <c r="B108" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="1" t="s">
         <v>228</v>
       </c>
     </row>
@@ -2389,7 +2359,7 @@
       <c r="B109" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2397,7 +2367,7 @@
       <c r="B110" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="1" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2440,6 +2410,7 @@
       <c r="C115" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="2" t="s">
@@ -2488,7 +2459,6 @@
       <c r="C121" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="2" t="s">
@@ -2579,49 +2549,49 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="B133" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="B138" s="2" t="s">
         <v>288</v>
       </c>
@@ -2647,140 +2617,98 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="B145" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>301</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="2" t="s">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="B148" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="2" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>309</v>
+        <v>118</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="B150" s="2" t="s">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>311</v>
+        <v>168</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
